--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:04</t>
+    <t xml:space="preserve">2026-09-17 14:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:01</t>
+    <t xml:space="preserve">2026-09-23 12:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:30</t>
+    <t xml:space="preserve">2026-10-02 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:13</t>
+    <t xml:space="preserve">2026-10-05 10:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -679,7 +679,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>791039.12</v>
+        <v>791039.13</v>
       </c>
     </row>
     <row r="9">
@@ -696,7 +696,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>778279.12</v>
+        <v>778279.13</v>
       </c>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>755731.62</v>
+        <v>755731.63</v>
       </c>
     </row>
     <row r="15">
@@ -951,7 +951,7 @@
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>706481.12</v>
+        <v>706481.13</v>
       </c>
     </row>
     <row r="25">
